--- a/LubanTools/DesignerConfigs/Datas/__enums_client__.xlsx
+++ b/LubanTools/DesignerConfigs/Datas/__enums_client__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\Fish\LubanTools\DesignerConfigs\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\AI-Unity-Framework\LubanTools\DesignerConfigs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636C8465-6423-4226-AF87-0C48EAD7A83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1DB125-5E59-4B7C-A296-AAFD88179DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26910" yWindow="1020" windowWidth="24315" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -92,20 +90,27 @@
     <t>注释</t>
   </si>
   <si>
-    <t>uiView.ViewName</t>
-  </si>
-  <si>
-    <t>UILoading</t>
-  </si>
-  <si>
-    <t>UILogin</t>
+    <t>GuideMaskType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Circle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,6 +136,13 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -174,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -190,6 +202,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -554,26 +569,32 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="6" t="s">
         <v>20</v>
       </c>
+      <c r="I4" s="6"/>
       <c r="J4" s="4">
-        <v>10000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="6" t="s">
         <v>21</v>
       </c>
       <c r="J5" s="4">
-        <v>10000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J6" s="4"/>
+      <c r="H6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="4">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J7" s="4"/>
